--- a/astro-site/public/dl/guia-panaderia-obrador/checklist-contratacion.xlsx
+++ b/astro-site/public/dl/guia-panaderia-obrador/checklist-contratacion.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratación" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contratación'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +44,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -74,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -83,10 +90,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -446,9 +464,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -465,10 +483,11 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -498,10 +517,6 @@
           <t>BÚSQUEDA PANADERO PRINCIPAL</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -725,10 +740,6 @@
           <t>AYUDANTE OBRADOR + BOLLERO</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -751,7 +762,6 @@
           <t>Tú</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -774,7 +784,6 @@
           <t>Tú</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -797,7 +806,6 @@
           <t>Tú + panadero</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -820,7 +828,6 @@
           <t>Gestor</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -828,10 +835,6 @@
           <t>DEPENDIENTES TIENDA</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -935,7 +938,6 @@
           <t>Gestor</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -943,10 +945,6 @@
           <t>FORMACIÓN EQUIPO Y APPCC</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1027,6 +1025,27 @@
         <is>
           <t>Coreografía mañana</t>
         </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C28">
+        <f>COUNTIF(A4:A26,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E28">
+        <f>COUNTIF(B4:B26,"?*")</f>
+        <v>19.0</v>
       </c>
     </row>
   </sheetData>
@@ -1037,6 +1056,25 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A18:E18"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A4:E26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A4="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A14 A15 A16 A17 A19 A20 A21 A22 A24 A25 A26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>